--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
